--- a/data/existing/판매중_납입주기정보_0312.xlsx
+++ b/data/existing/판매중_납입주기정보_0312.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -47,7 +47,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +62,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +84,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -103,6 +108,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
